--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_393_R43.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_393_R43.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9563</v>
+        <v>7.5415</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1918</v>
+        <v>5.8416</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7645</v>
+        <v>1.6999</v>
       </c>
       <c r="G2" t="n">
         <v>2.8558</v>
@@ -610,13 +610,13 @@
         <v>2.2747</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4654</v>
+        <v>1.0505</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0178</v>
+        <v>0.6676</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4476</v>
+        <v>0.3829</v>
       </c>
       <c r="V2" t="n">
         <v>2.7253</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>N. WILLIAMS-GOSS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8149</v>
+        <v>3.0414</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2048</v>
+        <v>3.1113</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6102</v>
+        <v>-0.0699</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2941</v>
+        <v>3.0949</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2566</v>
+        <v>0.7786</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5507</v>
+        <v>2.3163</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9055</v>
+        <v>5.2957</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0487</v>
+        <v>2.0838</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8568</v>
+        <v>3.2119</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6114</v>
+        <v>-2.2008</v>
       </c>
       <c r="N3" t="n">
         <v>-1.3052</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3062</v>
+        <v>-0.8956</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4549</v>
+        <v>-1.5923</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3648</v>
+        <v>-3.6396</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8198</v>
+        <v>2.0473</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3625</v>
+        <v>0.2903</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8024</v>
+        <v>0.2067</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5601</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7034</v>
+        <v>1.2485</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8617</v>
+        <v>1.2485</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1032</v>
+        <v>2.6407</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1046</v>
+        <v>2.1599</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.4809</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6083</v>
+        <v>0.2941</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1061</v>
+        <v>-0.2566</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7144</v>
+        <v>0.5507</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3714</v>
+        <v>1.9055</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9988</v>
+        <v>1.0487</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3702</v>
+        <v>0.8568</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2369</v>
+        <v>-1.6114</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8927</v>
+        <v>-1.3052</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6558</v>
+        <v>-0.3062</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6824</v>
+        <v>0.4549</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2275</v>
+        <v>-1.3648</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9099</v>
+        <v>1.8198</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7806</v>
+        <v>1.1883</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4551</v>
+        <v>0.7575</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3255</v>
+        <v>0.4308</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2485</v>
+        <v>0.7034</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2485</v>
+        <v>0.8617</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1583</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. WILLIAMS-GOSS</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0877</v>
+        <v>2.5378</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2223</v>
+        <v>1.4099</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1346</v>
+        <v>1.1278</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0949</v>
+        <v>-0.6083</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7786</v>
+        <v>0.1061</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3163</v>
+        <v>-0.7144</v>
       </c>
       <c r="J5" t="n">
-        <v>5.2957</v>
+        <v>-0.3714</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0838</v>
+        <v>0.9988</v>
       </c>
       <c r="L5" t="n">
-        <v>3.2119</v>
+        <v>-1.3702</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2008</v>
+        <v>-0.2369</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3052</v>
+        <v>-0.8927</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8956</v>
+        <v>0.6558</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5923</v>
+        <v>0.6824</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.6396</v>
+        <v>-0.2275</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0473</v>
+        <v>0.9099</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6633</v>
+        <v>1.2152</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6823</v>
+        <v>0.7604</v>
       </c>
       <c r="U5" t="n">
-        <v>0.019</v>
+        <v>0.4548</v>
       </c>
       <c r="V5" t="n">
         <v>1.2485</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. GIEDRAITIS</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1556</v>
+        <v>0.2257</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-0.5215</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1556</v>
+        <v>0.7472</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1556</v>
+        <v>-0.5406</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0.1002</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1556</v>
+        <v>-0.4404</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.8852</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.3968</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.4884</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1556</v>
+        <v>-1.4257</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.497</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1556</v>
+        <v>-0.9287</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.9099</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.0473</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.1437</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.2693</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.1256</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>D. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,19 +955,19 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0167</v>
+        <v>0.1556</v>
       </c>
       <c r="E7" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0047</v>
+        <v>0.1556</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1388</v>
+        <v>0.1556</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0169</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0.1556</v>
@@ -982,10 +982,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1388</v>
+        <v>0.1556</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0169</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0.1556</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1221</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1341</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1048</v>
+        <v>0.049</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.755</v>
+        <v>0.012</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6502</v>
+        <v>0.037</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5406</v>
+        <v>0.1388</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1002</v>
+        <v>-0.0169</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4404</v>
+        <v>0.1556</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8852</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3968</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4884</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4257</v>
+        <v>0.1388</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.497</v>
+        <v>-0.0169</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9287</v>
+        <v>0.1556</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9099</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0473</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4741</v>
+        <v>-0.0898</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5028</v>
+        <v>0.012</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0287</v>
+        <v>-0.1018</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.953</v>
+        <v>-1.0248</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2968</v>
+        <v>-2.5303</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3438</v>
+        <v>1.5054</v>
       </c>
       <c r="G9" t="n">
         <v>-2.2826</v>
@@ -1156,13 +1156,13 @@
         <v>1.3648</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0121</v>
+        <v>-0.0598</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2156</v>
+        <v>-0.0178</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2036</v>
+        <v>-0.0419</v>
       </c>
       <c r="V9" t="n">
         <v>1.0901</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.05</v>
+        <v>-2.0302</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5382</v>
+        <v>-2.4215</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4882</v>
+        <v>0.3912</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0572</v>
@@ -1234,13 +1234,13 @@
         <v>0.2275</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2203</v>
+        <v>-0.2005</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2035</v>
+        <v>-0.0867</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0168</v>
+        <v>-0.1138</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4116</v>
+        <v>-2.4565</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5126</v>
+        <v>-1.5575</v>
       </c>
       <c r="F11" t="n">
         <v>-0.899</v>
@@ -1312,10 +1312,10 @@
         <v>1.3648</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1197</v>
+        <v>-0.1646</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1438</v>
+        <v>0.0989</v>
       </c>
       <c r="U11" t="n">
         <v>-0.2635</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.875</v>
+        <v>-3.5808</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8602</v>
+        <v>-1.3721</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0148</v>
+        <v>-2.2087</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2902</v>
@@ -1390,13 +1390,13 @@
         <v>1.5923</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8701</v>
+        <v>1.1644</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7363</v>
+        <v>1.2244</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1339</v>
+        <v>-0.06</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5451</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.739999999999998</v>
+        <v>7.099400000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7727</v>
+        <v>4.1318</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9673</v>
+        <v>2.967399999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.648</v>
+        <v>-4.648000000000001</v>
       </c>
       <c r="H13" t="n">
         <v>-2.1474</v>
@@ -1447,13 +1447,13 @@
         <v>3.0756</v>
       </c>
       <c r="L13" t="n">
-        <v>1.198999999999999</v>
+        <v>1.199</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.922499999999999</v>
+        <v>-8.922500000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.222899999999999</v>
+        <v>-5.2229</v>
       </c>
       <c r="O13" t="n">
         <v>-3.6997</v>
@@ -1468,13 +1468,13 @@
         <v>13.6484</v>
       </c>
       <c r="S13" t="n">
-        <v>3.8912</v>
+        <v>4.2503</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9944</v>
+        <v>3.3537</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8968000000000002</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>5.222200000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. SILVA</t>
+          <t>N. DE COLO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6119</v>
+        <v>3.6281</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6321</v>
+        <v>1.6509</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9797</v>
+        <v>1.9773</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5469</v>
+        <v>3.9963</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9855</v>
+        <v>1.2437</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5614</v>
+        <v>2.7526</v>
       </c>
       <c r="J14" t="n">
-        <v>1.363</v>
+        <v>2.7074</v>
       </c>
       <c r="K14" t="n">
-        <v>1.363</v>
+        <v>1.1387</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.5687</v>
       </c>
       <c r="M14" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="O14" t="n">
         <v>1.1839</v>
       </c>
-      <c r="N14" t="n">
-        <v>0.6226</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.5614</v>
-      </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0.9099</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.2275</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3816</v>
+        <v>0.5417</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2692</v>
+        <v>0.0809</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1125</v>
+        <v>0.4608</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3167</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. DE COLO</t>
+          <t>C. SILVA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8565</v>
+        <v>2.8917</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0672</v>
+        <v>1.815</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7893</v>
+        <v>1.0767</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9963</v>
+        <v>2.5469</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2437</v>
+        <v>1.9855</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7526</v>
+        <v>0.5614</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7074</v>
+        <v>1.363</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1387</v>
+        <v>1.363</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5687</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.289</v>
+        <v>1.1839</v>
       </c>
       <c r="N15" t="n">
-        <v>0.105</v>
+        <v>0.6226</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1839</v>
+        <v>0.5614</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9099</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2275</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2299</v>
+        <v>0.6615</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5028</v>
+        <v>0.452</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2729</v>
+        <v>0.2094</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.3167</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.3167</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3865</v>
+        <v>0.8481</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6928</v>
+        <v>1.043</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3064</v>
+        <v>-0.1949</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3554</v>
@@ -1702,13 +1702,13 @@
         <v>2.0473</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9196</v>
+        <v>-0.458</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6344</v>
+        <v>-0.2842</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2851</v>
+        <v>-0.1737</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1583</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>T. BIBEROVIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0044</v>
+        <v>-0.1634</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1116</v>
+        <v>-1.1307</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1072</v>
+        <v>0.9673</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5444</v>
+        <v>2.1173</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.3186</v>
+        <v>0.8135</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7742</v>
+        <v>1.3038</v>
       </c>
       <c r="J17" t="n">
-        <v>0.572</v>
+        <v>2.826</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.2534</v>
+        <v>0.8435</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8254</v>
+        <v>1.9825</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1164</v>
+        <v>-0.7087</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0652</v>
+        <v>-0.03</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0512</v>
+        <v>-0.6787</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4549</v>
+        <v>-1.3648</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3648</v>
+        <v>-3.4121</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8198</v>
+        <v>2.0473</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.383</v>
+        <v>-0.9159</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2693</v>
+        <v>-0.5446</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.6523</v>
+        <v>-0.3713</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4768</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6352</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. BIBEROVIC</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.096</v>
+        <v>-0.2172</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3642</v>
+        <v>0.9443</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2681</v>
+        <v>-1.1614</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1173</v>
+        <v>-1.5444</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8135</v>
+        <v>-2.3186</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3038</v>
+        <v>0.7742</v>
       </c>
       <c r="J18" t="n">
-        <v>2.826</v>
+        <v>0.572</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8435</v>
+        <v>-1.2534</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9825</v>
+        <v>1.8254</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7087</v>
+        <v>-2.1164</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.03</v>
+        <v>-1.0652</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6787</v>
+        <v>-1.0512</v>
       </c>
       <c r="P18" t="n">
+        <v>0.4549</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-1.3648</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-3.4121</v>
-      </c>
       <c r="R18" t="n">
-        <v>2.0473</v>
+        <v>1.8198</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8485</v>
+        <v>-0.6045</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7781</v>
+        <v>0.102</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0704</v>
+        <v>-0.7065</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.4768</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.6352</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1583</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2004</v>
+        <v>-1.0315</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2855</v>
+        <v>-2.0521</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0852</v>
+        <v>1.0205</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4389</v>
@@ -1936,13 +1936,13 @@
         <v>0.2275</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1484</v>
+        <v>0.3172</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2873</v>
+        <v>-0.0538</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4357</v>
+        <v>0.3711</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. MELLI</t>
+          <t>W. BALDWIN IV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9505</v>
+        <v>-1.5553</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0448</v>
+        <v>-2.485</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9057</v>
+        <v>0.9296</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5719</v>
+        <v>1.3905</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2921</v>
+        <v>-0.3364</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2799</v>
+        <v>1.7269</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5505</v>
+        <v>0.6097</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2607</v>
+        <v>0.0387</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2899</v>
+        <v>0.571</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0214</v>
+        <v>0.7808</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0314</v>
+        <v>-0.3751</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.99</v>
+        <v>1.1559</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2275</v>
+        <v>-1.3648</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1374</v>
+        <v>-2.5022</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3648</v>
+        <v>1.1374</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7806999999999999</v>
+        <v>-0.4909</v>
       </c>
       <c r="T20" t="n">
-        <v>1.4848</v>
+        <v>-0.5925</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7040999999999999</v>
+        <v>0.1016</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3867</v>
+        <v>-1.0901</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1583</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5451</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. BALDWIN IV</t>
+          <t>N. MELLI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6257</v>
+        <v>-2.4109</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1854</v>
+        <v>-1.0954</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5597</v>
+        <v>-1.3155</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3905</v>
+        <v>-2.5719</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3364</v>
+        <v>-1.2921</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7269</v>
+        <v>-1.2799</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6097</v>
+        <v>-0.5505</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0387</v>
+        <v>-0.2607</v>
       </c>
       <c r="L21" t="n">
-        <v>0.571</v>
+        <v>-0.2899</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7808</v>
+        <v>-2.0214</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3751</v>
+        <v>-1.0314</v>
       </c>
       <c r="O21" t="n">
-        <v>1.1559</v>
+        <v>-0.99</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3648</v>
+        <v>0.2275</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.5022</v>
+        <v>-1.1374</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1374</v>
+        <v>1.3648</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5613</v>
+        <v>0.3203</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2929</v>
+        <v>0.4342</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2684</v>
+        <v>-0.1138</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0901</v>
+        <v>-0.3867</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0901</v>
+        <v>-0.5451</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9986</v>
+        <v>-2.7513</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8173</v>
+        <v>-1.4671</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1813</v>
+        <v>-1.2842</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5495</v>
@@ -2170,13 +2170,13 @@
         <v>0.9099</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1388</v>
+        <v>0.386</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5746</v>
+        <v>-0.2244</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7134</v>
+        <v>0.6105</v>
       </c>
       <c r="V22" t="n">
         <v>-3.2703</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7282</v>
+        <v>-2.8655</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.774</v>
+        <v>-0.1903</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9542</v>
+        <v>-2.6752</v>
       </c>
       <c r="G23" t="n">
         <v>0.0569</v>
@@ -2248,13 +2248,13 @@
         <v>1.5923</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3984</v>
+        <v>-0.5357</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8499</v>
+        <v>-0.2662</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5485</v>
+        <v>-0.2695</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4768</v>
@@ -2281,31 +2281,31 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.7401</v>
+        <v>-3.6272</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9675</v>
+        <v>-2.967400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.7728</v>
+        <v>-0.6597999999999993</v>
       </c>
       <c r="G24" t="n">
         <v>4.647800000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>2.1472</v>
+        <v>2.147199999999999</v>
       </c>
       <c r="I24" t="n">
         <v>2.5006</v>
       </c>
       <c r="J24" t="n">
-        <v>8.922499999999999</v>
+        <v>8.922500000000001</v>
       </c>
       <c r="K24" t="n">
         <v>5.2228</v>
       </c>
       <c r="L24" t="n">
-        <v>3.699599999999999</v>
+        <v>3.6996</v>
       </c>
       <c r="M24" t="n">
         <v>-4.2746</v>
@@ -2326,13 +2326,13 @@
         <v>11.3738</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.8912</v>
+        <v>-0.7783000000000003</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8966999999999997</v>
+        <v>-0.8966000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.9943</v>
+        <v>0.1186</v>
       </c>
       <c r="V24" t="n">
         <v>-5.2221</v>
